--- a/results/qwen3_8b/comparison_ToTRAG/ToTRAG_evaluated.xlsx
+++ b/results/qwen3_8b/comparison_ToTRAG/ToTRAG_evaluated.xlsx
@@ -505,37 +505,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2037735809480954</v>
+        <v>0.2802850306640112</v>
       </c>
       <c r="D2" t="n">
-        <v>1.730519463176098e-79</v>
+        <v>0.04389910330770813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5726922154426575</v>
+        <v>0.6463813781738281</v>
       </c>
       <c r="F2" t="n">
-        <v>27.79104591836736</v>
+        <v>49.51201581027669</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4304635761589404</v>
+        <v>1.364238410596027</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2513089005235602</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1836734693877551</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -548,37 +548,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09708737688754834</v>
+        <v>0.114754096855684</v>
       </c>
       <c r="D3" t="n">
-        <v>1.902237782330245e-155</v>
+        <v>8.709768942723901e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4620912075042725</v>
+        <v>0.4636981785297394</v>
       </c>
       <c r="F3" t="n">
-        <v>28.62210798122067</v>
+        <v>9.884166666666715</v>
       </c>
       <c r="G3" t="n">
-        <v>5.073394495412844</v>
+        <v>5.954128440366972</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2043010752688172</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="4">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2460317413151928</v>
+        <v>0.2996254633068216</v>
       </c>
       <c r="D4" t="n">
-        <v>5.219478241687084e-79</v>
+        <v>0.01901847649876204</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5399104952812195</v>
+        <v>0.5807259082794189</v>
       </c>
       <c r="F4" t="n">
-        <v>37.91352906050957</v>
+        <v>55.81330039525693</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6217948717948718</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="H4" t="n">
         <v>0.5</v>
@@ -615,13 +615,13 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3243243243243243</v>
       </c>
     </row>
     <row r="5">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.156996583188622</v>
+        <v>0.1783439447748388</v>
       </c>
       <c r="D5" t="n">
-        <v>2.098152133550718e-156</v>
+        <v>0.005446929611769897</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6534578204154968</v>
+        <v>0.5241946578025818</v>
       </c>
       <c r="F5" t="n">
-        <v>36.4156730769231</v>
+        <v>25.23000000000005</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4108019639934534</v>
+        <v>0.486088379705401</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2950819672131147</v>
+        <v>0.3012048192771085</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2391304347826087</v>
+        <v>0.1566265060240964</v>
       </c>
     </row>
     <row r="6">
@@ -677,22 +677,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3247863202337644</v>
+        <v>0.2407407365706448</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01992435169682143</v>
+        <v>2.282216633601617e-79</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6595125794410706</v>
+        <v>0.5687358379364014</v>
       </c>
       <c r="F6" t="n">
-        <v>53.39331250000001</v>
+        <v>37.45538461538465</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5678160919540229</v>
+        <v>0.4597701149425287</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -704,10 +704,10 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.1397849462365592</v>
       </c>
     </row>
     <row r="7">
@@ -720,37 +720,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2247190977838811</v>
+        <v>0.1614906796071236</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009973721376269843</v>
+        <v>0.0002373577558022702</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6286501288414001</v>
+        <v>0.6024760603904724</v>
       </c>
       <c r="F7" t="n">
-        <v>-52.6211764705882</v>
+        <v>-6.796126027397264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2522548734361362</v>
+        <v>0.2900785568810009</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1652173913043478</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M7" t="n">
-        <v>0.53125</v>
+        <v>0.4845360824742268</v>
       </c>
     </row>
     <row r="8">
@@ -763,37 +763,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.07604562506903388</v>
+        <v>0.2043343611728284</v>
       </c>
       <c r="D8" t="n">
-        <v>8.122503374890562e-161</v>
+        <v>0.003580694026239782</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5455583930015564</v>
+        <v>0.6190401315689087</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.315467479674766</v>
+        <v>25.44431721798136</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1965277777777778</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3292682926829268</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="9">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1581920871216765</v>
+        <v>0.1758241723036168</v>
       </c>
       <c r="D9" t="n">
-        <v>3.89003801738445e-157</v>
+        <v>8.008054613384905e-157</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5182662010192871</v>
+        <v>0.5668753981590271</v>
       </c>
       <c r="F9" t="n">
-        <v>50.70362211221124</v>
+        <v>40.48591176470592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2236384704519119</v>
+        <v>0.2734646581691773</v>
       </c>
       <c r="H9" t="n">
         <v>0.125</v>
@@ -833,10 +833,10 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3287671232876712</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1358024691358025</v>
       </c>
     </row>
     <row r="10">
@@ -849,19 +849,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1056338001500199</v>
+        <v>0.1628664460626638</v>
       </c>
       <c r="D10" t="n">
-        <v>1.394605555319197e-158</v>
+        <v>2.140753119986657e-80</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5722618699073792</v>
+        <v>0.582069456577301</v>
       </c>
       <c r="F10" t="n">
-        <v>29.26333333333335</v>
+        <v>43.62325091575093</v>
       </c>
       <c r="G10" t="n">
-        <v>0.212962962962963</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="H10" t="n">
         <v>0.3125</v>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.325</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2079207920792079</v>
+        <v>0.09722222222222221</v>
       </c>
     </row>
     <row r="11">
@@ -892,22 +892,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1564245779630786</v>
+        <v>0.1889763743443487</v>
       </c>
       <c r="D11" t="n">
-        <v>7.551042687299704e-158</v>
+        <v>6.432609166628714e-157</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5625163912773132</v>
+        <v>0.5794017314910889</v>
       </c>
       <c r="F11" t="n">
-        <v>40.02130645161293</v>
+        <v>35.70607142857145</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2203389830508475</v>
+        <v>0.2837616183706944</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -919,10 +919,10 @@
         <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1588785046728972</v>
+        <v>0.1836734693877551</v>
       </c>
     </row>
     <row r="12">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2210796875056338</v>
+        <v>0.2739725981404684</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004668335673030102</v>
+        <v>0.06200097980716292</v>
       </c>
       <c r="E12" t="n">
-        <v>0.65522301197052</v>
+        <v>0.6635017991065979</v>
       </c>
       <c r="F12" t="n">
-        <v>35.73416666666668</v>
+        <v>46.73448717948722</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3758542141230068</v>
+        <v>0.6007972665148064</v>
       </c>
       <c r="H12" t="n">
         <v>0.3333333333333333</v>
@@ -956,16 +956,16 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.247191011235955</v>
+        <v>0.2945736434108527</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1608391608391608</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="13">
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1288515377827995</v>
+        <v>0.1658031052323553</v>
       </c>
       <c r="D13" t="n">
-        <v>5.119788514303341e-158</v>
+        <v>7.10711879349888e-81</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5463192462921143</v>
+        <v>0.6234800219535828</v>
       </c>
       <c r="F13" t="n">
-        <v>38.38505494505497</v>
+        <v>31.70302631578949</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2039911308203991</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="H13" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1005,10 +1005,10 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="14">
@@ -1021,19 +1021,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1730279859539396</v>
+        <v>0.1303116117985058</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002124415352444144</v>
+        <v>5.763632549867579e-158</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5984796285629272</v>
+        <v>0.5841918587684631</v>
       </c>
       <c r="F14" t="n">
-        <v>40.87176804286167</v>
+        <v>27.69384615384618</v>
       </c>
       <c r="G14" t="n">
-        <v>0.365</v>
+        <v>0.2433333333333333</v>
       </c>
       <c r="H14" t="n">
         <v>0.3</v>
@@ -1042,16 +1042,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.3272727272727273</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2086330935251799</v>
+        <v>0.2125984251968504</v>
       </c>
     </row>
     <row r="15">
@@ -1064,19 +1064,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2694300468200489</v>
+        <v>0.2716049335467155</v>
       </c>
       <c r="D15" t="n">
-        <v>0.04233597443220442</v>
+        <v>0.06168908678404924</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6549957394599915</v>
+        <v>0.6621700525283813</v>
       </c>
       <c r="F15" t="n">
-        <v>66.35845368916799</v>
+        <v>66.5904166666667</v>
       </c>
       <c r="G15" t="n">
-        <v>1.13682092555332</v>
+        <v>0.7947686116700201</v>
       </c>
       <c r="H15" t="n">
         <v>0.5</v>
@@ -1088,13 +1088,13 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.46875</v>
+        <v>0.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2452830188679246</v>
+        <v>0.1596638655462185</v>
       </c>
     </row>
     <row r="16">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.334728028504403</v>
+        <v>0.2953586448282862</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02719889876789828</v>
+        <v>4.143346747104959e-155</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6745786070823669</v>
+        <v>0.6433549523353577</v>
       </c>
       <c r="F16" t="n">
-        <v>54.39610759493675</v>
+        <v>51.55000000000004</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8972895863052782</v>
+        <v>0.8801711840228246</v>
       </c>
       <c r="H16" t="n">
         <v>0.4</v>
@@ -1131,13 +1131,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2771084337349398</v>
+        <v>0.3950617283950617</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="17">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2417582367588457</v>
+        <v>0.307692302735662</v>
       </c>
       <c r="D17" t="n">
-        <v>6.923169578399921e-79</v>
+        <v>4.483793999855553e-155</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6635465621948242</v>
+        <v>0.6779084801673889</v>
       </c>
       <c r="F17" t="n">
-        <v>65.86748931623936</v>
+        <v>50.62711233885818</v>
       </c>
       <c r="G17" t="n">
-        <v>1.19758064516129</v>
+        <v>0.8830645161290323</v>
       </c>
       <c r="H17" t="n">
         <v>0.2857142857142857</v>
@@ -1171,16 +1171,16 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2755102040816326</v>
+        <v>0.3132530120481928</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3449781659388647</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="18">
@@ -1193,22 +1193,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1545064352453536</v>
+        <v>0.198412695068106</v>
       </c>
       <c r="D18" t="n">
-        <v>7.329163753806349e-05</v>
+        <v>0.001537731997565385</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5975859761238098</v>
+        <v>0.6199045181274414</v>
       </c>
       <c r="F18" t="n">
-        <v>42.52500000000001</v>
+        <v>50.2376315789474</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1647196261682243</v>
+        <v>0.2605140186915888</v>
       </c>
       <c r="H18" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1754385964912281</v>
+        <v>0.2934782608695652</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1752577319587629</v>
+        <v>0.2452830188679246</v>
       </c>
     </row>
     <row r="19">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.121387279103044</v>
+        <v>0.1437908464810544</v>
       </c>
       <c r="D19" t="n">
-        <v>2.862751418642962e-156</v>
+        <v>8.508076552407284e-82</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6129412055015564</v>
+        <v>0.5815699100494385</v>
       </c>
       <c r="F19" t="n">
-        <v>4.490693363520592</v>
+        <v>16.95392156862749</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4792353328938695</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -1263,10 +1263,10 @@
         <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.2407407407407407</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2244897959183673</v>
+        <v>0.09677419354838709</v>
       </c>
     </row>
     <row r="20">
@@ -1279,37 +1279,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1924398598344375</v>
+        <v>0.2291021634874293</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002754883808062679</v>
+        <v>0.004646776935916677</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6416764259338379</v>
+        <v>0.5817007422447205</v>
       </c>
       <c r="F20" t="n">
-        <v>51.70795698924732</v>
+        <v>49.96476190476193</v>
       </c>
       <c r="G20" t="n">
-        <v>0.220014194464159</v>
+        <v>0.3151171043293116</v>
       </c>
       <c r="H20" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3134328358208955</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.126984126984127</v>
       </c>
     </row>
     <row r="21">
@@ -1322,19 +1322,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1111111084659747</v>
+        <v>0.102893887847727</v>
       </c>
       <c r="D21" t="n">
-        <v>5.193780808598403e-83</v>
+        <v>2.312405001485916e-158</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5604392886161804</v>
+        <v>0.4981350302696228</v>
       </c>
       <c r="F21" t="n">
-        <v>28.23966666666669</v>
+        <v>30.47756147540989</v>
       </c>
       <c r="G21" t="n">
-        <v>0.175070821529745</v>
+        <v>0.1807365439093484</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1343,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0339425587467363</v>
+        <v>0.05511811023622047</v>
       </c>
     </row>
     <row r="22">
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.3436754128969418</v>
+        <v>0.3359374950000763</v>
       </c>
       <c r="D22" t="n">
-        <v>0.05294600622677436</v>
+        <v>0.07053867871481319</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6309255957603455</v>
+        <v>0.6660435795783997</v>
       </c>
       <c r="F22" t="n">
-        <v>43.69674661866304</v>
+        <v>47.30143659711078</v>
       </c>
       <c r="G22" t="n">
-        <v>0.703030303030303</v>
+        <v>1.118181818181818</v>
       </c>
       <c r="H22" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2605633802816901</v>
+        <v>0.2712765957446808</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.5633187772925764</v>
       </c>
     </row>
     <row r="23">
@@ -1408,37 +1408,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3326885834688297</v>
+        <v>0.279441113360664</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04283608159216823</v>
+        <v>0.006602789951994124</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6378268599510193</v>
+        <v>0.6492375135421753</v>
       </c>
       <c r="F23" t="n">
-        <v>35.1320666666667</v>
+        <v>21.45194612794617</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5548920532843362</v>
+        <v>0.4598070739549839</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2214765100671141</v>
+        <v>0.2357142857142857</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5804195804195804</v>
+        <v>0.3269230769230769</v>
       </c>
     </row>
     <row r="24">
@@ -1451,22 +1451,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.314049581875555</v>
+        <v>0.2488038227513107</v>
       </c>
       <c r="D24" t="n">
-        <v>4.317821519005071e-155</v>
+        <v>1.109142043699342e-78</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6371414065361023</v>
+        <v>0.6110427975654602</v>
       </c>
       <c r="F24" t="n">
-        <v>42.95136039250673</v>
+        <v>41.06107843137258</v>
       </c>
       <c r="G24" t="n">
-        <v>1.225806451612903</v>
+        <v>1.004608294930876</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1475,13 +1475,13 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3119266055045872</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3693693693693694</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="25">
@@ -1494,22 +1494,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.2527472480394881</v>
+        <v>0.3410138198933934</v>
       </c>
       <c r="D25" t="n">
-        <v>6.182703348071608e-79</v>
+        <v>0.03496693890036816</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6571572422981262</v>
+        <v>0.6924597024917603</v>
       </c>
       <c r="F25" t="n">
-        <v>26.96450653120468</v>
+        <v>42.0577097902098</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6817496229260935</v>
+        <v>0.9079939668174962</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1521,10 +1521,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2280701754385965</v>
+        <v>0.3048780487804878</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1791044776119403</v>
+        <v>0.358974358974359</v>
       </c>
     </row>
     <row r="26">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3648648602675311</v>
+        <v>0.2564102516477647</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02483428507458189</v>
+        <v>5.254232059758959e-79</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6959307193756104</v>
+        <v>0.643599271774292</v>
       </c>
       <c r="F26" t="n">
-        <v>40.12</v>
+        <v>35.00192307692311</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6273830155979203</v>
+        <v>0.6672443674176777</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -1564,10 +1564,10 @@
         <v>0.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -1580,37 +1580,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.278846149090699</v>
+        <v>0.3041474605831511</v>
       </c>
       <c r="D27" t="n">
-        <v>2.084154085234521e-155</v>
+        <v>1.002007873606135e-78</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6353515982627869</v>
+        <v>0.6967757344245911</v>
       </c>
       <c r="F27" t="n">
-        <v>38.83097706032288</v>
+        <v>27.20235772357725</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6716826265389877</v>
+        <v>0.6949384404924761</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2463768115942029</v>
+        <v>0.3382352941176471</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2134831460674157</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="28">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.3246073250108276</v>
+        <v>0.3482142807146843</v>
       </c>
       <c r="D28" t="n">
-        <v>1.493969587489462e-78</v>
+        <v>0.06131338182016789</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6791049838066101</v>
+        <v>0.7270402908325195</v>
       </c>
       <c r="F28" t="n">
-        <v>49.63168010752693</v>
+        <v>44.13137800687289</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7727272727272727</v>
+        <v>1.053030303030303</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -1650,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2708333333333334</v>
+        <v>0.3406593406593407</v>
       </c>
     </row>
     <row r="29">
@@ -1666,22 +1666,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.2890173360887434</v>
+        <v>0.3290043241618411</v>
       </c>
       <c r="D29" t="n">
-        <v>1.373248971716225e-78</v>
+        <v>0.03606300935643239</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6453489065170288</v>
+        <v>0.705970823764801</v>
       </c>
       <c r="F29" t="n">
-        <v>53.77121621621623</v>
+        <v>52.49662105263161</v>
       </c>
       <c r="G29" t="n">
-        <v>0.875</v>
+        <v>1.418402777777778</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -1690,13 +1690,13 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.2452830188679245</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3023255813953489</v>
+        <v>0.3577981651376147</v>
       </c>
     </row>
     <row r="30">
@@ -1709,37 +1709,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.09756097365556221</v>
+        <v>0.08108107993882398</v>
       </c>
       <c r="D30" t="n">
-        <v>2.073574161459504e-155</v>
+        <v>1.686106711860657e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4949854910373688</v>
+        <v>0.4581261873245239</v>
       </c>
       <c r="F30" t="n">
-        <v>40.23166666666668</v>
+        <v>37.54832317073172</v>
       </c>
       <c r="G30" t="n">
-        <v>4.11</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
         <v>0.5</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.2950819672131147</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="31">
@@ -1752,37 +1752,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1086956504087902</v>
+        <v>0.1509433934069064</v>
       </c>
       <c r="D31" t="n">
-        <v>2.204506820391453e-155</v>
+        <v>2.659276018264461e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4693386256694794</v>
+        <v>0.5454714894294739</v>
       </c>
       <c r="F31" t="n">
-        <v>46.86125000000001</v>
+        <v>12.31171428571432</v>
       </c>
       <c r="G31" t="n">
-        <v>5.087378640776699</v>
+        <v>3.184466019417476</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.162303664921466</v>
       </c>
     </row>
     <row r="32">
@@ -1795,19 +1795,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.06399999866368003</v>
+        <v>0.073529410528763</v>
       </c>
       <c r="D32" t="n">
-        <v>1.389479870686276e-155</v>
+        <v>1.512466137089683e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3869301676750183</v>
+        <v>0.4342751502990723</v>
       </c>
       <c r="F32" t="n">
-        <v>54.14497505632445</v>
+        <v>42.94238991295447</v>
       </c>
       <c r="G32" t="n">
-        <v>7.36</v>
+        <v>7.81</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -1819,13 +1819,13 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3372093023255814</v>
+        <v>0.3047619047619048</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.1964285714285714</v>
       </c>
     </row>
     <row r="33">
@@ -1838,22 +1838,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1958041911389311</v>
+        <v>0.251748247082987</v>
       </c>
       <c r="D33" t="n">
-        <v>3.45933709758742e-155</v>
+        <v>4.295154518309647e-155</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6131397485733032</v>
+        <v>0.619636595249176</v>
       </c>
       <c r="F33" t="n">
-        <v>57.17044642857144</v>
+        <v>67.63898395721927</v>
       </c>
       <c r="G33" t="n">
-        <v>1.46814404432133</v>
+        <v>1.656509695290859</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -1862,13 +1862,13 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>0.282051282051282</v>
+        <v>0.2676056338028169</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2079207920792079</v>
+        <v>0.2253521126760563</v>
       </c>
     </row>
     <row r="34">
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1686746946842794</v>
+        <v>0.2857142808721729</v>
       </c>
       <c r="D34" t="n">
-        <v>1.482225049885071e-232</v>
+        <v>1.38982761256313e-78</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5662921071052551</v>
+        <v>0.6029443740844727</v>
       </c>
       <c r="F34" t="n">
-        <v>36.25755649717516</v>
+        <v>35.11720724907065</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4709302325581395</v>
+        <v>1.406976744186047</v>
       </c>
       <c r="H34" t="n">
         <v>0.4</v>
@@ -1905,13 +1905,13 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2093023255813954</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.4565217391304348</v>
       </c>
     </row>
     <row r="35">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.2608695603353918</v>
+        <v>0.2405063244506089</v>
       </c>
       <c r="D35" t="n">
-        <v>0.04488671857282235</v>
+        <v>0.02777353716385257</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6748611927032471</v>
+        <v>0.6474072337150574</v>
       </c>
       <c r="F35" t="n">
-        <v>41.53360639972024</v>
+        <v>41.02083333333334</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7495621716287215</v>
+        <v>0.6120840630472855</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -1951,10 +1951,10 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.32</v>
+        <v>0.336734693877551</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.3103448275862069</v>
       </c>
     </row>
     <row r="36">
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.2426778192678701</v>
+        <v>0.2524916895711968</v>
       </c>
       <c r="D36" t="n">
-        <v>0.06903062197415055</v>
+        <v>6.554962806708901e-79</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6834411025047302</v>
+        <v>0.6158535480499268</v>
       </c>
       <c r="F36" t="n">
-        <v>17.14422705314013</v>
+        <v>34.87059288537552</v>
       </c>
       <c r="G36" t="n">
-        <v>1.206022187004754</v>
+        <v>1.787638668779715</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -1991,13 +1991,13 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.34375</v>
+        <v>0.2662337662337662</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3798449612403101</v>
+        <v>0.4797687861271676</v>
       </c>
     </row>
     <row r="37">
@@ -2010,37 +2010,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.2108433685121209</v>
+        <v>0.1850533758437711</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02547509243889352</v>
+        <v>6.314783638207477e-79</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6541558504104614</v>
+        <v>0.5938338041305542</v>
       </c>
       <c r="F37" t="n">
-        <v>44.98877137274062</v>
+        <v>38.76456043956046</v>
       </c>
       <c r="G37" t="n">
-        <v>1.219512195121951</v>
+        <v>0.7730646871686108</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.261437908496732</v>
+        <v>0.25</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5744680851063829</v>
+        <v>0.2156862745098039</v>
       </c>
     </row>
     <row r="38">
@@ -2053,22 +2053,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.201058196686543</v>
+        <v>0.2229299314763278</v>
       </c>
       <c r="D38" t="n">
-        <v>9.737500401119624e-156</v>
+        <v>8.476391991707779e-79</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6039879322052002</v>
+        <v>0.6034459471702576</v>
       </c>
       <c r="F38" t="n">
-        <v>15.07338235294122</v>
+        <v>31.96179054054056</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5407503234152652</v>
+        <v>1.410090556274256</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2080,10 +2080,10 @@
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.1757575757575758</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1588785046728972</v>
+        <v>0.3277310924369747</v>
       </c>
     </row>
     <row r="39">
@@ -2096,19 +2096,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.2519684990265981</v>
+        <v>0.234309618462562</v>
       </c>
       <c r="D39" t="n">
-        <v>0.04427100204850371</v>
+        <v>4.11235187953323e-155</v>
       </c>
       <c r="E39" t="n">
-        <v>0.651585578918457</v>
+        <v>0.6167111396789551</v>
       </c>
       <c r="F39" t="n">
-        <v>51.17286866201999</v>
+        <v>23.99470163703575</v>
       </c>
       <c r="G39" t="n">
-        <v>1.278761061946903</v>
+        <v>1.255162241887906</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -2117,16 +2117,16 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.3027522935779817</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3197278911564626</v>
+        <v>0.3359375</v>
       </c>
     </row>
     <row r="40">
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.2260869520967865</v>
+        <v>0.2418300603596908</v>
       </c>
       <c r="D40" t="n">
-        <v>1.854559965655109e-79</v>
+        <v>1.457028417329153e-78</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5178161263465881</v>
+        <v>0.6025745868682861</v>
       </c>
       <c r="F40" t="n">
-        <v>36.52914473684211</v>
+        <v>52.51057878151263</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5077092511013216</v>
+        <v>1.13215859030837</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -2166,10 +2166,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.303030303030303</v>
+        <v>0.265625</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.4573643410852714</v>
       </c>
     </row>
     <row r="41">
@@ -2182,22 +2182,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.2249240086381316</v>
+        <v>0.0507246362140307</v>
       </c>
       <c r="D41" t="n">
-        <v>5.429398294875774e-80</v>
+        <v>5.86409911537489e-163</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5529953837394714</v>
+        <v>0.4579188525676727</v>
       </c>
       <c r="F41" t="n">
-        <v>46.67366854384554</v>
+        <v>39.49229885057474</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3045267489711934</v>
+        <v>0.1296296296296296</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -2209,10 +2209,10 @@
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2950819672131147</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="42">
@@ -2225,22 +2225,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2288135547371446</v>
+        <v>0.2926829221072114</v>
       </c>
       <c r="D42" t="n">
-        <v>6.57725023597135e-79</v>
+        <v>0.02334892277116938</v>
       </c>
       <c r="E42" t="n">
-        <v>0.562541663646698</v>
+        <v>0.6065421104431152</v>
       </c>
       <c r="F42" t="n">
-        <v>39.94182629107985</v>
+        <v>40.86000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6377142857142857</v>
+        <v>0.6697142857142857</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -2249,13 +2249,13 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2560975609756098</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3749999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -2268,19 +2268,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.2080536863744877</v>
+        <v>0.2363112341951184</v>
       </c>
       <c r="D43" t="n">
-        <v>4.574655955439486e-155</v>
+        <v>7.310763335123578e-79</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6469773650169373</v>
+        <v>0.6416423916816711</v>
       </c>
       <c r="F43" t="n">
-        <v>44.14719696969701</v>
+        <v>38.06052650052655</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7998146431881371</v>
+        <v>1.048192771084337</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -2289,16 +2289,16 @@
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2920353982300885</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="M43" t="n">
-        <v>0.162303664921466</v>
+        <v>0.2458100558659218</v>
       </c>
     </row>
     <row r="44">
@@ -2311,37 +2311,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.2246376763508192</v>
+        <v>0.2990654155646782</v>
       </c>
       <c r="D44" t="n">
-        <v>2.957452411974128e-155</v>
+        <v>0.06535170365509098</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5641837120056152</v>
+        <v>0.7102271318435669</v>
       </c>
       <c r="F44" t="n">
-        <v>35.52250000000001</v>
+        <v>48.0510974443078</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8105625717566016</v>
+        <v>1.013777267508611</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2966101694915254</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2248062015503876</v>
+        <v>0.393939393939394</v>
       </c>
     </row>
     <row r="45">
@@ -2354,22 +2354,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2986822803167491</v>
+        <v>0.2478386128727919</v>
       </c>
       <c r="D45" t="n">
-        <v>0.005858677697764014</v>
+        <v>0.003330175202092506</v>
       </c>
       <c r="E45" t="n">
-        <v>0.626672625541687</v>
+        <v>0.6281514167785645</v>
       </c>
       <c r="F45" t="n">
-        <v>39.44922194457067</v>
+        <v>34.03243821500308</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2920208390457911</v>
+        <v>0.3035371538250617</v>
       </c>
       <c r="H45" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -2378,13 +2378,13 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2816901408450704</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.3220338983050848</v>
       </c>
     </row>
     <row r="46">
@@ -2397,25 +2397,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.1705426330603209</v>
+        <v>0.2513812117613932</v>
       </c>
       <c r="D46" t="n">
-        <v>9.410118253528093e-05</v>
+        <v>0.02842566423318661</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6249567866325378</v>
+        <v>0.6354157328605652</v>
       </c>
       <c r="F46" t="n">
-        <v>41.86512012012014</v>
+        <v>55.7096306818182</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1855441705898643</v>
+        <v>0.3373026862364996</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2424,10 +2424,10 @@
         <v>0.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2298850574712644</v>
+        <v>0.2808219178082192</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.6226415094339623</v>
       </c>
     </row>
     <row r="47">
@@ -2440,22 +2440,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.2510460218202588</v>
+        <v>0.3204225307707425</v>
       </c>
       <c r="D47" t="n">
-        <v>6.516607705595573e-80</v>
+        <v>0.02074628763542984</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6245467662811279</v>
+        <v>0.6796901822090149</v>
       </c>
       <c r="F47" t="n">
-        <v>42.82380952380956</v>
+        <v>32.26650825082513</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2534874451972898</v>
+        <v>0.4850538062973296</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2464,13 +2464,13 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2746478873239437</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2622950819672131</v>
+        <v>0.477124183006536</v>
       </c>
     </row>
     <row r="48">
@@ -2483,37 +2483,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.2333333284543211</v>
+        <v>0.2236842055263159</v>
       </c>
       <c r="D48" t="n">
-        <v>1.123899409227765e-78</v>
+        <v>4.167924894556696e-155</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6476296186447144</v>
+        <v>0.6185465455055237</v>
       </c>
       <c r="F48" t="n">
-        <v>32.99285714285716</v>
+        <v>46.47245121951221</v>
       </c>
       <c r="G48" t="n">
-        <v>1.381156316916488</v>
+        <v>1.019271948608137</v>
       </c>
       <c r="H48" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1346153846153846</v>
+        <v>0.1752577319587629</v>
       </c>
     </row>
     <row r="49">
@@ -2526,37 +2526,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.1733333284835557</v>
+        <v>0.1874999950500001</v>
       </c>
       <c r="D49" t="n">
-        <v>5.738497806296087e-79</v>
+        <v>1.564995262624393e-155</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6017470955848694</v>
+        <v>0.6401078104972839</v>
       </c>
       <c r="F49" t="n">
-        <v>24.33625000000004</v>
+        <v>37.18807692307692</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.861271676300578</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.1596638655462185</v>
       </c>
     </row>
     <row r="50">
@@ -2569,37 +2569,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.2857142807663474</v>
+        <v>0.1538461512426036</v>
       </c>
       <c r="D50" t="n">
-        <v>1.10902369222975e-78</v>
+        <v>5.336379554370441e-158</v>
       </c>
       <c r="E50" t="n">
-        <v>0.649381160736084</v>
+        <v>0.5437071919441223</v>
       </c>
       <c r="F50" t="n">
-        <v>35.34602564102568</v>
+        <v>46.81274509803924</v>
       </c>
       <c r="G50" t="n">
-        <v>1.344827586206897</v>
+        <v>0.2873563218390804</v>
       </c>
       <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
         <v>0.5</v>
       </c>
-      <c r="I50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.3157894736842105</v>
-      </c>
       <c r="M50" t="n">
-        <v>0.2028985507246377</v>
+        <v>0.05797101449275362</v>
       </c>
     </row>
     <row r="51">
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.29577464297684</v>
+        <v>0.3671874950076294</v>
       </c>
       <c r="D51" t="n">
-        <v>1.40176100383701e-78</v>
+        <v>0.05318774139695596</v>
       </c>
       <c r="E51" t="n">
-        <v>0.634158730506897</v>
+        <v>0.664139986038208</v>
       </c>
       <c r="F51" t="n">
-        <v>44.31494774919616</v>
+        <v>21.35137500000002</v>
       </c>
       <c r="G51" t="n">
-        <v>1.25832223701731</v>
+        <v>1.086551264980027</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -2633,16 +2633,16 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.3174603174603174</v>
+        <v>0.2336448598130841</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4392523364485982</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="52">
@@ -2655,25 +2655,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.2455089778168812</v>
+        <v>0.1594202872245852</v>
       </c>
       <c r="D52" t="n">
-        <v>3.407991521845531e-79</v>
+        <v>1.335095064155259e-157</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6236441135406494</v>
+        <v>0.5645071864128113</v>
       </c>
       <c r="F52" t="n">
-        <v>52.71924735111438</v>
+        <v>39.86342857142861</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4314720812182741</v>
+        <v>0.2059463379260334</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2682,10 +2682,10 @@
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="53">
@@ -2698,37 +2698,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.3603603558433772</v>
+        <v>0.3749999953233688</v>
       </c>
       <c r="D53" t="n">
-        <v>0.04679951705481336</v>
+        <v>0.03338087509600714</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6791532039642334</v>
+        <v>0.6651744842529297</v>
       </c>
       <c r="F53" t="n">
-        <v>39.58948446528373</v>
+        <v>35.30533967391307</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5096051227321238</v>
+        <v>0.6013874066168623</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3089430894308943</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M53" t="n">
-        <v>0.452054794520548</v>
+        <v>0.388888888888889</v>
       </c>
     </row>
     <row r="54">
@@ -2741,37 +2741,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.2910052860558215</v>
+        <v>0.3428571380349388</v>
       </c>
       <c r="D54" t="n">
-        <v>0.06899407273030436</v>
+        <v>0.08414974269172384</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6660365462303162</v>
+        <v>0.6761053204536438</v>
       </c>
       <c r="F54" t="n">
-        <v>37.73903483309147</v>
+        <v>43.7644774590164</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8366445916114791</v>
+        <v>0.6769683590875644</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2147651006711409</v>
+        <v>0.2822580645161291</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4244604316546763</v>
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="55">
@@ -2784,25 +2784,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2322946131130176</v>
+        <v>0.04528301686009265</v>
       </c>
       <c r="D55" t="n">
-        <v>0.01058202302624076</v>
+        <v>3.396921629371405e-239</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6578117609024048</v>
+        <v>0.5777973532676697</v>
       </c>
       <c r="F55" t="n">
-        <v>23.14378947368425</v>
+        <v>-67.21749999999997</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4870633893919793</v>
+        <v>0.1966364812419146</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3157894736842105</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -2811,10 +2811,10 @@
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2403846153846154</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2391304347826087</v>
+        <v>0.05660377358490565</v>
       </c>
     </row>
     <row r="56">
@@ -2827,37 +2827,37 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.09420289672757828</v>
+        <v>0.2239999955205689</v>
       </c>
       <c r="D56" t="n">
-        <v>1.595125071640276e-239</v>
+        <v>1.850791334670095e-79</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5541946887969971</v>
+        <v>0.6431059837341309</v>
       </c>
       <c r="F56" t="n">
-        <v>31.10813725490198</v>
+        <v>29.25229508196725</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1544352265475431</v>
+        <v>0.4767070835992342</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1139240506329114</v>
+        <v>0.2481203007518797</v>
       </c>
     </row>
     <row r="57">
@@ -2870,19 +2870,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.2675367008268378</v>
+        <v>0.2618657898993093</v>
       </c>
       <c r="D57" t="n">
-        <v>0.01055434144634028</v>
+        <v>0.005945899370026579</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6141224503517151</v>
+        <v>0.6275182962417603</v>
       </c>
       <c r="F57" t="n">
-        <v>51.36713793103448</v>
+        <v>42.95492300049679</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3552722260509993</v>
+        <v>0.3242591316333563</v>
       </c>
       <c r="H57" t="n">
         <v>0.3333333333333333</v>
@@ -2894,13 +2894,13 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2063492063492063</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
@@ -2913,37 +2913,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.1517857102427456</v>
+        <v>0.2380952331039188</v>
       </c>
       <c r="D58" t="n">
-        <v>1.117533984565559e-79</v>
+        <v>9.320458944274172e-79</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5478999018669128</v>
+        <v>0.6378589272499084</v>
       </c>
       <c r="F58" t="n">
-        <v>17.29523255813953</v>
+        <v>26.06043860713419</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4362850971922246</v>
+        <v>1.163066954643629</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="L58" t="n">
-        <v>0.25</v>
+        <v>0.2534246575342466</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.4623655913978494</v>
       </c>
     </row>
     <row r="59">
@@ -2956,37 +2956,37 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2134831420275218</v>
+        <v>0.2535211218091649</v>
       </c>
       <c r="D59" t="n">
-        <v>1.151793102877015e-79</v>
+        <v>0.02103885804841746</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5395029187202454</v>
+        <v>0.5801204442977905</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.349080459770079</v>
+        <v>29.81879310344829</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4393939393939394</v>
+        <v>1.21969696969697</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.2781954887218045</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="60">
@@ -2999,37 +2999,37 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2780410700483417</v>
+        <v>0.275752769192161</v>
       </c>
       <c r="D60" t="n">
-        <v>0.01450794484019664</v>
+        <v>0.03097275134609704</v>
       </c>
       <c r="E60" t="n">
-        <v>0.6303671598434448</v>
+        <v>0.6212339401245117</v>
       </c>
       <c r="F60" t="n">
-        <v>35.22313725490199</v>
+        <v>31.86911612599906</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4454926624737945</v>
+        <v>0.5310971348707197</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L60" t="n">
-        <v>0.245398773006135</v>
+        <v>0.2298136645962733</v>
       </c>
       <c r="M60" t="n">
-        <v>0.458128078817734</v>
+        <v>0.6716417910447761</v>
       </c>
     </row>
     <row r="61">
@@ -3042,37 +3042,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.1363636329350322</v>
+        <v>0.1212121183147843</v>
       </c>
       <c r="D61" t="n">
-        <v>2.775544290086747e-155</v>
+        <v>5.434222959060843e-79</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5160923004150391</v>
+        <v>0.4991749823093414</v>
       </c>
       <c r="F61" t="n">
-        <v>22.2842391304348</v>
+        <v>54.79465184049081</v>
       </c>
       <c r="G61" t="n">
-        <v>2.506072874493927</v>
+        <v>3.396761133603239</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.313953488372093</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1772151898734177</v>
+        <v>0.3233082706766917</v>
       </c>
     </row>
     <row r="62">
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.2068965470585613</v>
+        <v>0.1526717507907466</v>
       </c>
       <c r="D62" t="n">
-        <v>1.525420446765144e-155</v>
+        <v>2.041150620072487e-155</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4929231405258179</v>
+        <v>0.6374655365943909</v>
       </c>
       <c r="F62" t="n">
-        <v>49.72587264150945</v>
+        <v>36.98561538461541</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6525</v>
+        <v>0.9225</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -3112,10 +3112,10 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1</v>
+        <v>0.1379310344827586</v>
       </c>
     </row>
     <row r="63">
@@ -3128,37 +3128,37 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.2279792703267203</v>
+        <v>0.1752577276474653</v>
       </c>
       <c r="D63" t="n">
-        <v>2.698386591461445e-79</v>
+        <v>4.999600024564736e-156</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5203997492790222</v>
+        <v>0.5119909644126892</v>
       </c>
       <c r="F63" t="n">
-        <v>49.29145833333337</v>
+        <v>47.07205399061036</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5202231520223152</v>
+        <v>0.4909344490934449</v>
       </c>
       <c r="H63" t="n">
         <v>0.25</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3125</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1150442477876106</v>
+        <v>0.08256880733944955</v>
       </c>
     </row>
     <row r="64">
@@ -3171,19 +3171,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.3092783456052716</v>
+        <v>0.2583025782029112</v>
       </c>
       <c r="D64" t="n">
-        <v>3.551652806380462e-155</v>
+        <v>0.02514370313572025</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6491305232048035</v>
+        <v>0.6672975420951843</v>
       </c>
       <c r="F64" t="n">
-        <v>50.49725000000004</v>
+        <v>39.89187180796733</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8819672131147541</v>
+        <v>1.567213114754098</v>
       </c>
       <c r="H64" t="n">
         <v>0.75</v>
@@ -3195,13 +3195,13 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3582089552238806</v>
+        <v>0.336</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1911764705882353</v>
+        <v>0.2537313432835821</v>
       </c>
     </row>
     <row r="65">
@@ -3214,19 +3214,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.259999995018</v>
+        <v>0.2743362783271988</v>
       </c>
       <c r="D65" t="n">
-        <v>1.005424523454277e-78</v>
+        <v>0.0414682325579625</v>
       </c>
       <c r="E65" t="n">
-        <v>0.592657208442688</v>
+        <v>0.6343826055526733</v>
       </c>
       <c r="F65" t="n">
-        <v>53.62308327825514</v>
+        <v>53.11579184100421</v>
       </c>
       <c r="G65" t="n">
-        <v>1.280561122244489</v>
+        <v>1.547094188376753</v>
       </c>
       <c r="H65" t="n">
         <v>1</v>
@@ -3238,13 +3238,13 @@
         <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.35</v>
       </c>
       <c r="M65" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2156862745098039</v>
       </c>
     </row>
     <row r="66">
@@ -3257,19 +3257,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.2292490070021404</v>
+        <v>0.3294117598351404</v>
       </c>
       <c r="D66" t="n">
-        <v>0.02219715813919129</v>
+        <v>0.03913077173831421</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5993309020996094</v>
+        <v>0.6727531552314758</v>
       </c>
       <c r="F66" t="n">
-        <v>34.30561919504646</v>
+        <v>56.7633287292818</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8682559598494354</v>
+        <v>0.7641154328732748</v>
       </c>
       <c r="H66" t="n">
         <v>0.6666666666666666</v>
@@ -3281,13 +3281,13 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.3037974683544304</v>
       </c>
       <c r="M66" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="67">
@@ -3300,37 +3300,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.2317596517010813</v>
+        <v>0.2809917305539239</v>
       </c>
       <c r="D67" t="n">
-        <v>1.243482204168198e-78</v>
+        <v>0.03998047557520408</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6747742891311646</v>
+        <v>0.6766796112060547</v>
       </c>
       <c r="F67" t="n">
-        <v>50.6308424908425</v>
+        <v>37.66029411764708</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8178082191780822</v>
+        <v>0.8945205479452055</v>
       </c>
       <c r="H67" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3294117647058823</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M67" t="n">
-        <v>0.101123595505618</v>
+        <v>0.2366412213740458</v>
       </c>
     </row>
     <row r="68">
@@ -3343,37 +3343,37 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.1161290305098855</v>
+        <v>0.2051282020216963</v>
       </c>
       <c r="D68" t="n">
-        <v>4.762308121761521e-79</v>
+        <v>9.656944879633529e-79</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4599381983280182</v>
+        <v>0.5352259278297424</v>
       </c>
       <c r="F68" t="n">
-        <v>7.826848635235763</v>
+        <v>13.3386363636364</v>
       </c>
       <c r="G68" t="n">
-        <v>7.007874015748031</v>
+        <v>3.204724409448819</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L68" t="n">
-        <v>0.272</v>
+        <v>0.3559322033898305</v>
       </c>
       <c r="M68" t="n">
-        <v>0.3617021276595745</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
   </sheetData>
